--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/07_vendors_contracts.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/07_vendors_contracts.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Ra57f869da2d14468"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R4d303b08461344dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rcb95d053de85472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Re804e25b9cb34ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R0f7e62f9c91e46d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rb1f14924473e47c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R583ec597ff154045"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R4cc837386e4b45d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R117fe03a75f1423c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R27784851bf8f404b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R8e3791e76fd947c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R350dde0bee7e4528"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -626,7 +626,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fbf1d66ba3448a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3206d4e721e5427d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -797,7 +797,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N6" s="78" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate ServiceNow (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -844,7 +844,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N7" s="79" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Fiserv (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O7" s="45" t="str">
         <x:v>High</x:v>
@@ -891,7 +891,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for FIS (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O8" t="str">
         <x:v>Medium</x:v>
@@ -938,7 +938,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Salesforce (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O9" t="str">
         <x:v>High</x:v>
@@ -985,7 +985,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Azure (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O10" t="str">
         <x:v>Medium</x:v>
@@ -1032,7 +1032,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate FIS (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O11" t="str">
         <x:v>High</x:v>
@@ -1079,7 +1079,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm ServiceNow (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O12" t="str">
         <x:v>Medium</x:v>
@@ -1126,7 +1126,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Fiserv (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O13" t="str">
         <x:v>High</x:v>
@@ -1173,7 +1173,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Informatica (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O14" t="str">
         <x:v>Medium</x:v>
@@ -1220,7 +1220,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Azure (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O15" t="str">
         <x:v>High</x:v>
@@ -1267,7 +1267,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate NICE (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O16" t="str">
         <x:v>Medium</x:v>
@@ -1314,7 +1314,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Experian (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O17" t="str">
         <x:v>High</x:v>
@@ -1361,7 +1361,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for ServiceNow (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O18" t="str">
         <x:v>Medium</x:v>
@@ -1408,7 +1408,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Fiserv (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O19" t="str">
         <x:v>High</x:v>
@@ -1455,7 +1455,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Experian (record 15) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O20" t="str">
         <x:v>Medium</x:v>
@@ -1502,7 +1502,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Databricks (record 16) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O21" t="str">
         <x:v>High</x:v>
@@ -1549,7 +1549,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Databricks (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O22" t="str">
         <x:v>Medium</x:v>
@@ -1596,7 +1596,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Accenture Managed Services (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O23" t="str">
         <x:v>High</x:v>
@@ -1643,7 +1643,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Salesforce (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O24" t="str">
         <x:v>Medium</x:v>
@@ -1690,7 +1690,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Informatica (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O25" t="str">
         <x:v>High</x:v>
@@ -1737,7 +1737,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Accenture Managed Services (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O26" t="str">
         <x:v>Medium</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm NICE (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O27" t="str">
         <x:v>High</x:v>
@@ -1831,7 +1831,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Databricks (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O28" t="str">
         <x:v>Medium</x:v>
@@ -1878,7 +1878,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Accenture Managed Services (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O29" t="str">
         <x:v>High</x:v>
@@ -1925,7 +1925,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Experian (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O30" t="str">
         <x:v>Medium</x:v>
@@ -1972,7 +1972,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Databricks (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O31" t="str">
         <x:v>High</x:v>
@@ -2019,7 +2019,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Snowflake (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O32" t="str">
         <x:v>Medium</x:v>
@@ -2066,7 +2066,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for ServiceNow (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O33" t="str">
         <x:v>High</x:v>
@@ -2113,7 +2113,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Salesforce (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O34" t="str">
         <x:v>Medium</x:v>
@@ -2160,7 +2160,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Informatica (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O35" t="str">
         <x:v>High</x:v>
@@ -2207,7 +2207,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Accenture Managed Services (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O36" t="str">
         <x:v>Medium</x:v>
@@ -2254,7 +2254,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm NICE (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O37" t="str">
         <x:v>High</x:v>
@@ -2301,7 +2301,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate FIS (record 33) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O38" t="str">
         <x:v>Medium</x:v>
@@ -2348,7 +2348,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Salesforce (record 34) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O39" t="str">
         <x:v>High</x:v>
@@ -2395,7 +2395,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Salesforce (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O40" t="str">
         <x:v>Medium</x:v>
@@ -2442,7 +2442,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Informatica (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O41" t="str">
         <x:v>High</x:v>
@@ -2489,7 +2489,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N42" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm ServiceNow (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O42" t="str">
         <x:v>Medium</x:v>
@@ -2536,7 +2536,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N43" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Fiserv (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O43" t="str">
         <x:v>High</x:v>
@@ -2583,7 +2583,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N44" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile FIS (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O44" t="str">
         <x:v>Medium</x:v>
@@ -2630,7 +2630,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N45" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Salesforce (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O45" t="str">
         <x:v>High</x:v>
@@ -2677,7 +2677,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N46" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate TransUnion (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O46" t="str">
         <x:v>Medium</x:v>
@@ -2724,7 +2724,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N47" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Snowflake (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O47" t="str">
         <x:v>High</x:v>
@@ -2771,7 +2771,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N48" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for TransUnion (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O48" t="str">
         <x:v>Medium</x:v>
@@ -2818,7 +2818,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N49" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Snowflake (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O49" t="str">
         <x:v>High</x:v>
@@ -2842,7 +2842,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R979a4ab37a584411"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref0b37e5db9a4b8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2917,7 +2917,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c137961c688454d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfe2d3eb83bd489f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3101,7 +3101,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd100675b67884bb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5586f55358914b19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3171,7 +3171,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf986c3e1486b42cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R163c72c425ed447c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3281,7 +3281,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46faf35d7f1d4666"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6565ddfd06c741cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>